--- a/patient_registration_form_templates/043_hospice_care_discharge_form--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/043_hospice_care_discharge_form--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'acetaminophen'}</t>
+          <t>acetaminophen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Acetaminophen'}</t>
+          <t>Acetaminophen</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'albuterol'}</t>
+          <t>albuterol</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Albuterol'}</t>
+          <t>Albuterol</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'alprazolam'}</t>
+          <t>alprazolam</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Alprazolam'}</t>
+          <t>Alprazolam</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'atorvastatin'}</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Atorvastatin'}</t>
+          <t>Atorvastatin</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'atenolol'}</t>
+          <t>atenolol</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Atenolol'}</t>
+          <t>Atenolol</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'azithromycin'}</t>
+          <t>azithromycin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Azithromycin'}</t>
+          <t>Azithromycin</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'aripiprazole'}</t>
+          <t>aripiprazole</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Aripiprazole'}</t>
+          <t>Aripiprazole</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cetirizine'}</t>
+          <t>cetirizine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Cetirizine'}</t>
+          <t>Cetirizine</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'ceftriaxone'}</t>
+          <t>ceftriaxone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Ceftriaxone'}</t>
+          <t>Ceftriaxone</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'cephalexin'}</t>
+          <t>cephalexin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Cephalexin'}</t>
+          <t>Cephalexin</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'clonazepam'}</t>
+          <t>clonazepam</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Clonazepam'}</t>
+          <t>Clonazepam</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'clobetasol'}</t>
+          <t>clobetasol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Clobetasol'}</t>
+          <t>Clobetasol</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
